--- a/Result/profitability/2466.xlsx
+++ b/Result/profitability/2466.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0.08125</v>
+        <v>0.1075</v>
       </c>
       <c r="N2" t="n">
-        <v>6.24125</v>
+        <v>7.96875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.15</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08624999999999999</v>
+        <v>0.01625</v>
       </c>
       <c r="N3" t="n">
-        <v>6.49</v>
+        <v>9.391249999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.22</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04125</v>
+        <v>0.10375</v>
       </c>
       <c r="N4" t="n">
-        <v>6.991250000000001</v>
+        <v>10.29375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.3</v>
       </c>
       <c r="M5" t="n">
-        <v>0.06375</v>
+        <v>0.1675</v>
       </c>
       <c r="N5" t="n">
-        <v>8.126250000000001</v>
+        <v>12.02375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>-0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>0.16</v>
+        <v>-0.11875</v>
       </c>
       <c r="N6" t="n">
-        <v>9.475</v>
+        <v>12.9925</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1125</v>
+        <v>-0.01749999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>10.67</v>
+        <v>14.9175</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,16 +1391,16 @@
         <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005000000000000008</v>
+        <v>0.003750000000000024</v>
       </c>
       <c r="N8" t="n">
-        <v>12.9725</v>
+        <v>15.795</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.28</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03625000000000001</v>
+        <v>0.03625000000000003</v>
       </c>
       <c r="N9" t="n">
         <v>14.76125</v>
@@ -1645,7 +1645,7 @@
         <v>0.08</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04500000000000001</v>
+        <v>0.04500000000000003</v>
       </c>
       <c r="N10" t="n">
         <v>14.33125</v>
@@ -1772,7 +1772,7 @@
         <v>0.06</v>
       </c>
       <c r="M11" t="n">
-        <v>0.07125000000000001</v>
+        <v>0.07125000000000002</v>
       </c>
       <c r="N11" t="n">
         <v>13.60375</v>
@@ -1899,7 +1899,7 @@
         <v>0.14</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06125000000000001</v>
+        <v>0.06125000000000003</v>
       </c>
       <c r="N12" t="n">
         <v>13.82</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2466</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>239</v>
+      </c>
+      <c r="D75" t="n">
+        <v>168</v>
+      </c>
+      <c r="E75" t="n">
+        <v>71</v>
+      </c>
+      <c r="F75" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="N75" t="n">
+        <v>7.35375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.009999999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>22.58</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>3.140472878998609</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.024691358024691</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-22.11347517730497</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
